--- a/data/trans_orig/IP07_C16_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP07_C16_2023-Clase-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si han sufrido cyberbulling en 2023 (tasa de respuesta: 99,48%)</t>
+          <t>Menores según si han sufrido cyberbulling en su colegio/instituto o fuera de él en 2023 (tasa de respuesta: 99,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>39879</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>28719</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>25483</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>30114</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>94,2%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>83,59%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>98,78%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>39124</t>
+          <t>30138</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>26390</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>31680</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>82,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>67843</t>
+          <t>70017</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>64740</t>
+          <t>65916</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>69235</t>
+          <t>71560</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,51%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1768</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>373</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>5004</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>5,8%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,22%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>16,41%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1892</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>350</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5640</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1768</t>
+          <t>1892</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>349</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4871</t>
+          <t>5993</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>8,33%</t>
         </is>
       </c>
     </row>
@@ -1059,57 +1059,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>39879</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>39879</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>39879</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>30487</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>30487</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>30487</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>39124</t>
+          <t>32030</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>39124</t>
+          <t>32030</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39124</t>
+          <t>32030</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>69611</t>
+          <t>71909</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>69611</t>
+          <t>71909</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>69611</t>
+          <t>71909</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1181,27 +1181,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>27683</t>
+          <t>31605</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>24018</t>
+          <t>27537</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>29168</t>
+          <t>33195</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>82,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1216,27 +1216,27 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>30837</t>
+          <t>29283</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>27227</t>
+          <t>26020</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>32438</t>
+          <t>30771</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>84,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>58520</t>
+          <t>60888</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>54456</t>
+          <t>56700</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>60700</t>
+          <t>63131</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,69%</t>
         </is>
       </c>
     </row>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1485</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5150</t>
+          <t>5658</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1601</t>
+          <t>1488</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5211</t>
+          <t>4751</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>3086</t>
+          <t>3078</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>906</t>
+          <t>835</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7150</t>
+          <t>7266</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,36%</t>
         </is>
       </c>
     </row>
@@ -1520,17 +1520,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>29168</t>
+          <t>33195</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29168</t>
+          <t>33195</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>29168</t>
+          <t>33195</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>32438</t>
+          <t>30771</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>32438</t>
+          <t>30771</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>32438</t>
+          <t>30771</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>61606</t>
+          <t>63966</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>61606</t>
+          <t>63966</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>61606</t>
+          <t>63966</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1632,74 +1632,74 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>25709</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>21655</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>26973</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>95,31%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>80,28%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>14549</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>15567</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>26372</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>22529</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>27685</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>95,26%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>81,38%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>52</t>
@@ -1707,27 +1707,27 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>40922</t>
+          <t>41276</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>36705</t>
+          <t>37019</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>42235</t>
+          <t>42540</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>86,91%</t>
+          <t>87,02%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1858,107 +1858,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>5318</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>4,69%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>19,72%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>1313</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>5156</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>4,74%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1264</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>5521</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>2,97%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>18,62%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1313</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>5530</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>3,11%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>12,98%</t>
         </is>
       </c>
     </row>
@@ -1971,57 +1971,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>26973</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>26973</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>26973</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>14549</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>14549</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>14549</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>27685</t>
+          <t>15567</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>27685</t>
+          <t>15567</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>27685</t>
+          <t>15567</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>42235</t>
+          <t>42540</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>42235</t>
+          <t>42540</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>42235</t>
+          <t>42540</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2088,72 +2088,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>61961</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>47368</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>67295</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>89,26%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>68,24%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>96,95%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>36061</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>13470</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>62039</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>53,7%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>20,06%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>92,38%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>62244</t>
+          <t>36555</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>46195</t>
+          <t>28363</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>68640</t>
+          <t>40492</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>83,81%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>65,26%</t>
+          <t>65,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>98306</t>
+          <t>98516</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>54253</t>
+          <t>85269</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>127225</t>
+          <t>105632</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>71,27%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>75,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>93,46%</t>
         </is>
       </c>
     </row>
@@ -2201,72 +2201,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>5259</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>20730</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>7,58%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>29,86%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>28205</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>1310</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>52458</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>42,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>1,95%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>78,11%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>4105</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>850</t>
+          <t>831</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23172</t>
+          <t>14915</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>34343</t>
+          <t>9364</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3729</t>
+          <t>2735</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>79635</t>
+          <t>22765</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>57,73%</t>
+          <t>20,14%</t>
         </is>
       </c>
     </row>
@@ -2314,72 +2314,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>2194</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>622</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>6399</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>3,16%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>9,22%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>2889</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>7513</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>4,3%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>11,19%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>2955</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>711</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>6945</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>5293</t>
+          <t>5150</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1800</t>
+          <t>2104</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>10485</t>
+          <t>9978</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>8,83%</t>
         </is>
       </c>
     </row>
@@ -2427,57 +2427,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>69414</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>69414</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>69414</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>67155</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>67155</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>67155</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>70787</t>
+          <t>43616</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>70787</t>
+          <t>43616</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>70787</t>
+          <t>43616</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>137942</t>
+          <t>113030</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>137942</t>
+          <t>113030</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>137942</t>
+          <t>113030</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2544,72 +2544,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>56087</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>51863</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>57813</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>96,26%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>89,01%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>99,22%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>32759</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>29410</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>34188</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>94,65%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>84,97%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>98,78%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>57726</t>
+          <t>35981</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>53295</t>
+          <t>31953</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>59959</t>
+          <t>37471</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,32 +2619,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>90485</t>
+          <t>92067</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>85746</t>
+          <t>86050</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>93173</t>
+          <t>94345</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,18%</t>
         </is>
       </c>
     </row>
@@ -2657,107 +2657,107 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>1168</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>4406</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>3,37%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>1186</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>4456</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>3,13%</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>12,73%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>11,78%</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>1186</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>5130</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>1168</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>4313</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>1,23%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>5,34%</t>
         </is>
       </c>
     </row>
@@ -2770,72 +2770,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>2178</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>452</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>6402</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>3,74%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>10,99%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>683</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>3289</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>1,97%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>663</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>3691</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>1,75%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>9,5%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>2233</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>6664</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>3,72%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,32 +2845,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>2916</t>
+          <t>2841</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>707</t>
+          <t>705</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>7455</t>
+          <t>7349</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,65%</t>
         </is>
       </c>
     </row>
@@ -2883,57 +2883,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>58265</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>58265</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>58265</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>34610</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>34610</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>34610</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>59959</t>
+          <t>37830</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>59959</t>
+          <t>37830</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>59959</t>
+          <t>37830</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>94569</t>
+          <t>96094</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>94569</t>
+          <t>96094</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>94569</t>
+          <t>96094</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3005,27 +3005,27 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>29721</t>
+          <t>34879</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>27981</t>
+          <t>31189</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>30177</t>
+          <t>36521</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>85,4%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -3040,27 +3040,27 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>34385</t>
+          <t>32639</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>30048</t>
+          <t>30066</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>36068</t>
+          <t>33129</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>83,31%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3075,32 +3075,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>64105</t>
+          <t>67519</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>60466</t>
+          <t>63500</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>65809</t>
+          <t>69151</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,28%</t>
         </is>
       </c>
     </row>
@@ -3226,72 +3226,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>1642</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>5332</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>4,5%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>14,6%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>456</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>2196</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>1,51%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>490</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>3063</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>7,28%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>1683</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>6020</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>4,67%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,32 +3301,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>2139</t>
+          <t>2132</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>435</t>
+          <t>500</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5778</t>
+          <t>6151</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,83%</t>
         </is>
       </c>
     </row>
@@ -3339,57 +3339,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>36521</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>36521</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>36521</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>30177</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>30177</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>30177</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>36068</t>
+          <t>33129</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>36068</t>
+          <t>33129</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>36068</t>
+          <t>33129</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3414,17 +3414,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>66244</t>
+          <t>69651</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>66244</t>
+          <t>69651</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>66244</t>
+          <t>69651</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3456,72 +3456,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>286</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>250120</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>235646</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>256125</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>94,65%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>89,18%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>96,93%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>248</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>169491</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>106848</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>197305</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>82,22%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>51,83%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>95,71%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>286</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>250689</t>
+          <t>180162</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>228555</t>
+          <t>170267</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>257867</t>
+          <t>185555</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>88,25%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,32 +3531,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>420180</t>
+          <t>430282</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>336970</t>
+          <t>413262</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>449785</t>
+          <t>439682</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>88,98%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>96,17%</t>
         </is>
       </c>
     </row>
@@ -3569,107 +3569,107 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>5259</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>24294</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>1,99%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>9,19%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>29372</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>1832</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>95329</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>14,25%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>46,24%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>5291</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1583</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>28656</t>
+          <t>15757</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
+          <t>2,74%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>0,82%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>8,17%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>10550</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>3762</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>29180</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
           <t>2,31%</t>
         </is>
       </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>10,77%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>35511</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>4710</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>118842</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>7,52%</t>
-        </is>
-      </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>6,38%</t>
         </is>
       </c>
     </row>
@@ -3682,72 +3682,72 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>8869</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>4473</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>15002</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>3,36%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>1,69%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>5,68%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>7281</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>3619</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>12894</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>3,53%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>1,76%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>6,26%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>9234</t>
+          <t>7489</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>4945</t>
+          <t>3757</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>16287</t>
+          <t>13587</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,32 +3757,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>16516</t>
+          <t>16358</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>10160</t>
+          <t>10932</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>24691</t>
+          <t>24513</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -3795,57 +3795,57 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>264248</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>264248</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>264248</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
           <t>264</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>206145</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>206145</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>206145</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>266062</t>
+          <t>192942</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>266062</t>
+          <t>192942</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>266062</t>
+          <t>192942</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3870,17 +3870,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>472207</t>
+          <t>457190</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>472207</t>
+          <t>457190</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>472207</t>
+          <t>457190</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
